--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.176.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.176.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.176.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.176.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.176.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.176.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0176.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0176.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -598,11 +598,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 49</t>
@@ -610,7 +614,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -637,7 +641,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -700,7 +704,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -739,7 +743,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -751,7 +755,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -802,7 +806,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: cationsâ€™ &amp;c.,</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -851,11 +855,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ntmentâ€�, read</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       <c r="N13" s="1" t="inlineStr"/>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
       <c r="N14" s="1" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
       <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
       <c r="N16" s="1" t="inlineStr"/>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
